--- a/public/tabela_exemplo.xlsx
+++ b/public/tabela_exemplo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guilh\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9DECEF2-7569-4A86-802E-82D1DB1E10A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CD40802-72FE-42E4-909E-DADF82666AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="53">
   <si>
     <t>Data</t>
   </si>
@@ -113,12 +113,6 @@
   </si>
   <si>
     <t>FISIO. UNIFESP</t>
-  </si>
-  <si>
-    <t>FEFIS UNIMES</t>
-  </si>
-  <si>
-    <t>MED. VET. SÃO JUDAS</t>
   </si>
   <si>
     <t>FM</t>
@@ -622,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -845,7 +839,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>23</v>
@@ -864,370 +858,347 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="6">
+        <v>0.81944444444444442</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="7">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="6">
+        <v>0.88194444444444442</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="6">
+        <v>0.81944444444444442</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="7">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="6">
+        <v>0.88194444444444442</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="7">
+        <v>0.90972222222222221</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="7">
+        <v>0.8125</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="7">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="6">
         <v>0.875</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C24" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D24" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="3" t="s">
+      <c r="D25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6">
-        <v>0.81944444444444442</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="7">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="6">
-        <v>0.88194444444444442</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="6">
-        <v>0.81944444444444442</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" s="7">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B19" s="6">
-        <v>0.88194444444444442</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" s="7">
-        <v>0.90972222222222221</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="7">
-        <v>0.8125</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="6">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" s="7">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25" s="6">
-        <v>0.875</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G26" s="2" t="s">
+      <c r="G25" s="2" t="s">
         <v>13</v>
       </c>
     </row>

--- a/public/tabela_exemplo.xlsx
+++ b/public/tabela_exemplo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guilh\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CD40802-72FE-42E4-909E-DADF82666AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C236818-477D-4AF1-9E84-13A113355DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="75">
   <si>
     <t>Data</t>
   </si>
@@ -43,7 +43,7 @@
     <t>Fase</t>
   </si>
   <si>
-    <t>06/05/2025</t>
+    <t>05/05/2026</t>
   </si>
   <si>
     <t>19:00</t>
@@ -52,10 +52,10 @@
     <t>FSM</t>
   </si>
   <si>
-    <t>ODONTO S.JUDAS</t>
-  </si>
-  <si>
-    <t>ED. FIS. UNIFESP</t>
+    <t>MED UNIMES</t>
+  </si>
+  <si>
+    <t>MED VET UNIMES</t>
   </si>
   <si>
     <t>Poliesportivo - Unisanta</t>
@@ -64,128 +64,194 @@
     <t>Fase de Classificação</t>
   </si>
   <si>
+    <t>a seguir</t>
+  </si>
+  <si>
+    <t>NUTRIÇÃO UNISANTA</t>
+  </si>
+  <si>
+    <t>PSICO UNISANTOS</t>
+  </si>
+  <si>
+    <t>ADM UNISANTA</t>
+  </si>
+  <si>
+    <t>FARMACIA UNISANTA</t>
+  </si>
+  <si>
+    <t>BM</t>
+  </si>
+  <si>
+    <t>FEFESP UNISANTA</t>
+  </si>
+  <si>
+    <t>DIREITO UNISANTA</t>
+  </si>
+  <si>
+    <t>PSICO UNISANTA</t>
+  </si>
+  <si>
+    <t>ENG UNISANTA</t>
+  </si>
+  <si>
+    <t>VM</t>
+  </si>
+  <si>
+    <t>ED FISICA UNIFESP</t>
+  </si>
+  <si>
+    <t>FISIO UNISANTA</t>
+  </si>
+  <si>
+    <t>Laerte Gonçalves - Unisanta</t>
+  </si>
+  <si>
+    <t>MED UNAERP</t>
+  </si>
+  <si>
+    <t>SIST INFO UNISANTA</t>
+  </si>
+  <si>
+    <t>DIREITO UNIMES</t>
+  </si>
+  <si>
+    <t>ED FISICA UNAERP</t>
+  </si>
+  <si>
+    <t>FISIO UNIFESP</t>
+  </si>
+  <si>
+    <t>FM</t>
+  </si>
+  <si>
+    <t>BIOL UNISANTA</t>
+  </si>
+  <si>
+    <t>Centro de Treinamento - Unisanta</t>
+  </si>
+  <si>
+    <t>ADM STRONG</t>
+  </si>
+  <si>
+    <t>TECNO INFO UNISANTOS</t>
+  </si>
+  <si>
+    <t>FISIO UNAERP</t>
+  </si>
+  <si>
+    <t>FEFIS UNIMES</t>
+  </si>
+  <si>
+    <t>FF</t>
+  </si>
+  <si>
+    <t>DIREITO UNISANTOS</t>
+  </si>
+  <si>
+    <t>DIREITO ESAMC</t>
+  </si>
+  <si>
+    <t>Rebouças</t>
+  </si>
+  <si>
+    <t>COMUNIC UNISANTOS</t>
+  </si>
+  <si>
+    <t>ENG ESAMC</t>
+  </si>
+  <si>
+    <t>06/05/2026</t>
+  </si>
+  <si>
+    <t>TEC INFO ESAMC</t>
+  </si>
+  <si>
+    <t>TEC INFO UNISANTOS</t>
+  </si>
+  <si>
+    <t>ODONTO UNISANTA</t>
+  </si>
+  <si>
+    <t>CIEN DADOS FATEC</t>
+  </si>
+  <si>
+    <t>BIOMED UNISANTA</t>
+  </si>
+  <si>
     <t>FSF</t>
   </si>
   <si>
-    <t>DIREITO UNISANTOS</t>
+    <t>MED UNOESTE</t>
+  </si>
+  <si>
+    <t>NEGOCIOS ESAMC</t>
   </si>
   <si>
     <t>FAAC UNISANTA</t>
   </si>
   <si>
-    <t>SIST. INF. UNISANTA</t>
-  </si>
-  <si>
-    <t>NUTRIÇÃO UNIFESP</t>
-  </si>
-  <si>
-    <t>MED. UNAERP</t>
-  </si>
-  <si>
-    <t>BIOMED UNISANTA</t>
-  </si>
-  <si>
-    <t>MED. UNOESTE</t>
-  </si>
-  <si>
-    <t>ED. FIS. UNAERP</t>
-  </si>
-  <si>
-    <t>VM</t>
-  </si>
-  <si>
-    <t>MED UNOESTE</t>
-  </si>
-  <si>
-    <t>ADM. UNISANTA</t>
-  </si>
-  <si>
-    <t>Laerte Gonçalves - Unisanta</t>
-  </si>
-  <si>
-    <t>DIREITO UNISANTA</t>
-  </si>
-  <si>
-    <t>NUTRIÇÃO UNISANTA</t>
-  </si>
-  <si>
-    <t>ARQUIT. UNISANTA</t>
-  </si>
-  <si>
-    <t>FISIO. UNIFESP</t>
-  </si>
-  <si>
-    <t>FM</t>
-  </si>
-  <si>
-    <t>ED. FIS. FPG</t>
-  </si>
-  <si>
-    <t>ODONTO UNISANTA</t>
-  </si>
-  <si>
-    <t>Centro de Treinamento - Unisanta</t>
+    <t>ANALI SIST FATEC</t>
+  </si>
+  <si>
+    <t>NEGÓCIOS ESAMC</t>
+  </si>
+  <si>
+    <t>COMEX UNISANTA</t>
+  </si>
+  <si>
+    <t>Natação M/F</t>
+  </si>
+  <si>
+    <t>COMPETIÇÃO</t>
+  </si>
+  <si>
+    <t>Piscina Olímpica - Unisanta</t>
+  </si>
+  <si>
+    <t>07/05/2026</t>
   </si>
   <si>
     <t>FACECS UNISANTOS</t>
   </si>
   <si>
-    <t>ENG. FED. CUBATÃO</t>
-  </si>
-  <si>
-    <t>MED. VET SÃO JUDAS</t>
-  </si>
-  <si>
-    <t>DIREITO UNIMES</t>
-  </si>
-  <si>
-    <t>FF</t>
-  </si>
-  <si>
-    <t>ENG. UNISANTA</t>
-  </si>
-  <si>
-    <t>07/05/2025</t>
-  </si>
-  <si>
-    <t>COMUNIC. UNISANTOS</t>
-  </si>
-  <si>
-    <t>FISIO. UNIP</t>
-  </si>
-  <si>
-    <t>FISIO. UNISANTA</t>
-  </si>
-  <si>
-    <t>ENFERM. UNISANTA</t>
-  </si>
-  <si>
-    <t>ENG. FED CUBATÃO</t>
-  </si>
-  <si>
-    <t>SAUDE UNISANTOS</t>
-  </si>
-  <si>
-    <t>DIREITO ESAMC</t>
-  </si>
-  <si>
-    <t>MED. UNIMES</t>
-  </si>
-  <si>
-    <t>PSICO. UNISANTA</t>
-  </si>
-  <si>
-    <t>TEC. INF. UNISANTOS</t>
-  </si>
-  <si>
-    <t>20;30</t>
+    <t>ANALIS. SIST. FATEC</t>
+  </si>
+  <si>
+    <t>ANALIS SIST UNIP</t>
+  </si>
+  <si>
+    <t>VF</t>
+  </si>
+  <si>
+    <t>REL INT UNISANTA</t>
+  </si>
+  <si>
+    <t>TERAPIA OCUP UNISANTA</t>
+  </si>
+  <si>
+    <t>COMUNICAÇÃO ESAMC</t>
+  </si>
+  <si>
+    <t>08/05/2026</t>
+  </si>
+  <si>
+    <t>MED SÃO JUDAS</t>
+  </si>
+  <si>
+    <t>MED UNILUS</t>
+  </si>
+  <si>
+    <t>ANALI SIST UNIP</t>
+  </si>
+  <si>
+    <t>Legenda de Cores por Dia:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -195,7 +261,7 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
@@ -203,8 +269,17 @@
       <sz val="10"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -218,12 +293,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD6E4F0"/>
+        <fgColor rgb="FFDDEEFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFE2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -237,16 +322,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB0B0B0"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="FFB0B0B0"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="FFB0B0B0"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB0B0B0"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
       <diagonal/>
     </border>
@@ -254,7 +339,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -271,11 +356,30 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -616,18 +720,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="5" width="28" customWidth="1"/>
+    <col min="4" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="32" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -674,25 +778,25 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="6">
-        <v>0.81944444444444442</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="B3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -700,8 +804,8 @@
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="7">
-        <v>0.85416666666666663</v>
+      <c r="B4" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
@@ -720,25 +824,25 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="6">
-        <v>0.88194444444444442</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="B5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="D5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="E5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -746,17 +850,17 @@
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="7">
-        <v>0.90972222222222221</v>
+      <c r="B6" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>12</v>
@@ -766,25 +870,25 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="C7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="D7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="E7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="F7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -792,45 +896,45 @@
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="7">
-        <v>0.8125</v>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="6">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="5" t="s">
+      <c r="B9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="4" t="s">
+      <c r="E9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -839,19 +943,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -862,44 +966,44 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="6">
-        <v>0.81944444444444442</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="4" t="s">
+      <c r="E12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -907,301 +1011,1088 @@
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="7">
-        <v>0.85416666666666663</v>
+      <c r="B13" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="6">
-        <v>0.88194444444444442</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G14" s="4" t="s">
+      <c r="F14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E15" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="6">
-        <v>0.81944444444444442</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="5" t="s">
+      <c r="F16" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="7">
-        <v>0.85416666666666663</v>
+        <v>7</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="E17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="6">
-        <v>0.88194444444444442</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="4" t="s">
+      <c r="F18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="7">
-        <v>0.90972222222222221</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="F19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F19" s="3" t="s">
+      <c r="D21" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="7">
-        <v>0.8125</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="6">
-        <v>0.83333333333333337</v>
+        <v>46</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="E22" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F22" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B23" s="7">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="2" t="s">
+      <c r="F23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="6">
-        <v>0.875</v>
-      </c>
-      <c r="C24" s="4" t="s">
+      <c r="E31" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="16.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E47" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+      <c r="F47" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D52" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="E52" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B55" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D25" s="3" t="s">
+      <c r="C55" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E55" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="F55" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D57" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
+      <c r="E57" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:7" ht="16.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="16.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="16.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="16.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="16.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="65" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="66" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="67" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="68" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
